--- a/example/e.xlsx
+++ b/example/e.xlsx
@@ -1,38 +1,88 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Develoip\proojects\Antigravity\Word-Excel-templates\example\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8EA9CB6-BEFB-465A-BE83-4DC8EAF3688F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аркуш1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12345_Лист 2010_qwerty" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="123" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1Лист 2010" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист 20101" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
+    <sheet name="12345_Лист 2010_qwerty" sheetId="2" r:id="rId2"/>
+    <sheet name="123" sheetId="3" r:id="rId3"/>
+    <sheet name="1Лист 2010" sheetId="4" r:id="rId4"/>
+    <sheet name="Лист 20101" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+  <si>
+    <t>рынок
+цен
+за 
+такой-то год</t>
+  </si>
+  <si>
+    <t>Молоко</t>
+  </si>
+  <si>
+    <t>Картошка</t>
+  </si>
+  <si>
+    <t>Макароны</t>
+  </si>
+  <si>
+    <t>Итого</t>
+  </si>
+  <si>
+    <t>{2010}</t>
+  </si>
+  <si>
+    <t>Хлеб</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="204"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,91 +100,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -454,132 +446,97 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>рынок
-цен
-за 
-такой-то год</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="B3" t="n">
+    <row r="1" spans="1:2" ht="70">
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="B3">
         <v>2010</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Молоко</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TestValue</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
+    <row r="4" spans="1:2">
+      <c r="A4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Картошка</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
+    <row r="6" spans="1:2">
+      <c r="A6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Макароны</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
+    <row r="7" spans="1:2">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="B10" s="1" t="n"/>
+    <row r="9" spans="1:2">
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" s="1">
+        <f>SUM(B4:B7)</f>
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B5:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>рынок
-цен
-за 
-такой-то год</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
+    <row r="5" spans="2:7" ht="70">
+      <c r="B5" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3">
         <v>2010</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3">
         <v>5</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3">
         <v>2</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="9">
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>{2010}</t>
-        </is>
+    <row r="9" spans="2:7">
+      <c r="C9" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -588,39 +545,27 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
